--- a/reports/latest/Reports/Passed_Test_Cases.xlsx
+++ b/reports/latest/Reports/Passed_Test_Cases.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.192</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.004</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="164">
@@ -16007,7 +16007,7 @@
         </is>
       </c>
       <c r="G444" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="445">

--- a/reports/latest/Reports/Passed_Test_Cases.xlsx
+++ b/reports/latest/Reports/Passed_Test_Cases.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="6">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="8">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="9">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="10">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="11">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="16">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="17">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="19">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="20">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="21">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="22">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="23">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="24">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="25">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="26">
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="27">
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="28">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="29">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="30">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="31">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="32">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="33">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="34">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="35">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="36">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="37">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="38">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="39">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="40">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="41">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="42">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="94">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="95">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="97">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="164">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="166">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="203">
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="267">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="284">
@@ -13137,7 +13137,7 @@
         </is>
       </c>
       <c r="G362" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="363">
@@ -13172,7 +13172,7 @@
         </is>
       </c>
       <c r="G363" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G386" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -16007,7 +16007,7 @@
         </is>
       </c>
       <c r="G444" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="445">
@@ -16672,7 +16672,7 @@
         </is>
       </c>
       <c r="G463" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="464">
@@ -16777,7 +16777,7 @@
         </is>
       </c>
       <c r="G466" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467">

--- a/reports/latest/Reports/Passed_Test_Cases.xlsx
+++ b/reports/latest/Reports/Passed_Test_Cases.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="3">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="6">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="8">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="9">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="10">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="11">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="14">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="15">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="16">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="17">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="19">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="20">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="21">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="22">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="23">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="24">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="25">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="26">
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="27">
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="28">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="29">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="31">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="32">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="33">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="34">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="35">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="36">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="37">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="38">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="39">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="40">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="41">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="42">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="45">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="46">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="94">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="95">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="96">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="97">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="144">
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="146">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="164">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="166">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="203">
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="267">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="284">
@@ -13172,7 +13172,7 @@
         </is>
       </c>
       <c r="G363" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="364">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G386" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="387">
@@ -16672,7 +16672,7 @@
         </is>
       </c>
       <c r="G463" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="464">
@@ -16777,7 +16777,7 @@
         </is>
       </c>
       <c r="G466" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="467">

--- a/reports/latest/Reports/Passed_Test_Cases.xlsx
+++ b/reports/latest/Reports/Passed_Test_Cases.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.09</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="3">

--- a/reports/latest/Reports/Passed_Test_Cases.xlsx
+++ b/reports/latest/Reports/Passed_Test_Cases.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.243</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="3">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="6">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="8">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="9">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="10">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="11">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="16">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="17">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="19">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="20">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="21">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="22">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="24">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="40">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="94">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="95">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="97">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="164">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="166">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="203">
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="267">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="284">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G386" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -16777,7 +16777,7 @@
         </is>
       </c>
       <c r="G466" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467">

--- a/reports/latest/Reports/Passed_Test_Cases.xlsx
+++ b/reports/latest/Reports/Passed_Test_Cases.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.462</v>
+        <v>0.271</v>
       </c>
     </row>
     <row r="3">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="6">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="8">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="9">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="10">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="11">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="14">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="15">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="16">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="17">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="19">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="20">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="21">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="22">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="24">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="40">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="46">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="94">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="95">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="96">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="97">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="144">
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="146">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="164">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="166">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="203">
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="267">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="284">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G386" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="387">
@@ -16777,7 +16777,7 @@
         </is>
       </c>
       <c r="G466" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="467">

--- a/reports/latest/Reports/Passed_Test_Cases.xlsx
+++ b/reports/latest/Reports/Passed_Test_Cases.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.271</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="3">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="6">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="8">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="9">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="10">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="11">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="16">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="17">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="19">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="20">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="21">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="22">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="23">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="24">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="25">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="26">
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="27">
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="28">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="29">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="30">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="31">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="32">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="33">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="34">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="35">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="36">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="37">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="38">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="39">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="40">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="41">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="42">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="94">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="95">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="97">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="163">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="164">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="166">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="203">
@@ -9637,7 +9637,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="267">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="284">
@@ -13172,7 +13172,7 @@
         </is>
       </c>
       <c r="G363" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G386" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
@@ -16672,7 +16672,7 @@
         </is>
       </c>
       <c r="G463" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="464">
@@ -16777,7 +16777,7 @@
         </is>
       </c>
       <c r="G466" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="467">

--- a/reports/latest/Reports/Passed_Test_Cases.xlsx
+++ b/reports/latest/Reports/Passed_Test_Cases.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.252</v>
+        <v>0.08799999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="4">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="6">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="7">
@@ -712,7 +712,7 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="8">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="9">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="10">
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="11">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="15">
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="16">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="17">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="19">
@@ -1167,7 +1167,7 @@
         </is>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="21">
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="22">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="G22" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="23">
@@ -1272,7 +1272,7 @@
         </is>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="24">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="25">
@@ -1342,7 +1342,7 @@
         </is>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="26">
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="27">
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="G27" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="28">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="G28" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="29">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="30">
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="31">
@@ -1552,7 +1552,7 @@
         </is>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="32">
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="G32" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="33">
@@ -1622,7 +1622,7 @@
         </is>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="34">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="G34" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="35">
@@ -1692,7 +1692,7 @@
         </is>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="36">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="37">
@@ -1762,7 +1762,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="38">
@@ -1797,7 +1797,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="39">
@@ -1832,7 +1832,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="40">
@@ -1867,7 +1867,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="41">
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="42">
@@ -2007,7 +2007,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="45">
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="46">
@@ -3722,7 +3722,7 @@
         </is>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="94">
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="G95" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="96">
@@ -5472,7 +5472,7 @@
         </is>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="144">
@@ -5542,7 +5542,7 @@
         </is>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="146">
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="G162" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="163">
@@ -6172,7 +6172,7 @@
         </is>
       </c>
       <c r="G163" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="164">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="G165" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="166">
@@ -7537,7 +7537,7 @@
         </is>
       </c>
       <c r="G202" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="203">
@@ -9637,7 +9637,7 @@
         </is>
       </c>
       <c r="G262" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="263">
@@ -9777,7 +9777,7 @@
         </is>
       </c>
       <c r="G266" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="267">
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="G282" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="283">
@@ -10372,7 +10372,7 @@
         </is>
       </c>
       <c r="G283" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="284">
@@ -13172,7 +13172,7 @@
         </is>
       </c>
       <c r="G363" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="364">
@@ -16672,7 +16672,7 @@
         </is>
       </c>
       <c r="G463" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="464">

--- a/reports/latest/Reports/Passed_Test_Cases.xlsx
+++ b/reports/latest/Reports/Passed_Test_Cases.xlsx
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="3">
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="14">
@@ -1132,7 +1132,7 @@
         </is>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0.003</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="20">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.002</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="95">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
     </row>
     <row r="97">
@@ -13977,7 +13977,7 @@
         </is>
       </c>
       <c r="G386" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="387">
@@ -16777,7 +16777,7 @@
         </is>
       </c>
       <c r="G466" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="467">
